--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488198_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488198_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8607</v>
+        <v>2.1807</v>
       </c>
       <c r="E2" t="n">
         <v>3.3885</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5278</v>
+        <v>-1.2077</v>
       </c>
       <c r="G2" t="n">
         <v>-1.9765</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0791</v>
+        <v>0.3992</v>
       </c>
       <c r="T2" t="n">
         <v>-0.1716</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2507</v>
+        <v>0.5708</v>
       </c>
       <c r="V2" t="n">
         <v>2.8316</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3867</v>
+        <v>0.9949</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6016</v>
+        <v>-0.9933</v>
       </c>
       <c r="F3" t="n">
         <v>1.9883</v>
@@ -688,10 +688,10 @@
         <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0211</v>
+        <v>-0.3706</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2773</v>
+        <v>-0.669</v>
       </c>
       <c r="U3" t="n">
         <v>0.2984</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7331</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3257</v>
+        <v>0.4236</v>
       </c>
       <c r="F4" t="n">
         <v>0.4074</v>
@@ -766,10 +766,10 @@
         <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3706</v>
+        <v>-0.2726</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6566</v>
+        <v>-0.5586</v>
       </c>
       <c r="U4" t="n">
         <v>0.286</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5915</v>
+        <v>-2.1852</v>
       </c>
       <c r="E5" t="n">
-        <v>0.327</v>
+        <v>-0.8481</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9186</v>
+        <v>-1.3371</v>
       </c>
       <c r="G5" t="n">
         <v>1.4638</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8161</v>
+        <v>1.2224</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8454</v>
+        <v>0.6703</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9707</v>
+        <v>0.5521</v>
       </c>
       <c r="V5" t="n">
         <v>-2.8332</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0273</v>
+        <v>-2.3239</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6264</v>
+        <v>-1.4306</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4009</v>
+        <v>-0.8933</v>
       </c>
       <c r="G6" t="n">
         <v>-2.4595</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6354</v>
+        <v>0.3389</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.715</v>
+        <v>-0.5192</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3504</v>
+        <v>0.858</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9444</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.6818</v>
+        <v>-3.3126</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8749</v>
+        <v>-3.039</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8068</v>
+        <v>-0.2736</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9997</v>
+        <v>-3.188</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7514</v>
+        <v>-0.7457</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7511</v>
+        <v>-2.4423</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7184</v>
+        <v>-1.7613</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8635</v>
+        <v>-0.4556</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5819</v>
+        <v>-1.3057</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7187</v>
+        <v>-1.4267</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8878</v>
+        <v>-0.2901</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1692</v>
+        <v>-1.1366</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.1499</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.891</v>
+        <v>-1.4823</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0423</v>
+        <v>0.6895</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3867</v>
+        <v>0.2046</v>
       </c>
       <c r="U7" t="n">
-        <v>0.429</v>
+        <v>0.485</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5738</v>
+        <v>-0.6289</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2583</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7771</v>
+        <v>-3.7324</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6266</v>
+        <v>-4.1457</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1505</v>
+        <v>0.4133</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.188</v>
+        <v>-3.0018</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7457</v>
+        <v>0.531</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4423</v>
+        <v>-3.5329</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7613</v>
+        <v>-1.7439</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4556</v>
+        <v>0.2147</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3057</v>
+        <v>-1.9586</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4267</v>
+        <v>-1.258</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2901</v>
+        <v>0.3163</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1366</v>
+        <v>-1.5743</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4823</v>
+        <v>-2.2234</v>
       </c>
       <c r="R8" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2251</v>
+        <v>-0.1747</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.383</v>
+        <v>-0.1784</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6081</v>
+        <v>0.0037</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7139</v>
+        <v>-3.7797</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7333</v>
+        <v>-2.9729</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0194</v>
+        <v>-0.8068</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0018</v>
+        <v>0.9997</v>
       </c>
       <c r="H9" t="n">
-        <v>0.531</v>
+        <v>-1.7514</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.5329</v>
+        <v>2.7511</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7439</v>
+        <v>1.7184</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2147</v>
+        <v>-0.8635</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9586</v>
+        <v>2.5819</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.258</v>
+        <v>-0.7187</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3163</v>
+        <v>-0.8878</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5743</v>
+        <v>0.1692</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2234</v>
+        <v>-3.891</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1562</v>
+        <v>-0.0556</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.766</v>
+        <v>-0.4846</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3902</v>
+        <v>0.429</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.5738</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9011</v>
+        <v>-4.3851</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7558</v>
+        <v>-3.5599</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1453</v>
+        <v>-0.8252</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2578</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6073</v>
+        <v>-0.0914</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4414</v>
+        <v>-0.2456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1659</v>
+        <v>0.1542</v>
       </c>
       <c r="V10" t="n">
         <v>-3.1477</v>
@@ -1273,7 +1273,7 @@
         <v>-13.1774</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5348</v>
+        <v>-2.5347</v>
       </c>
       <c r="G11" t="n">
         <v>-10.5264</v>
@@ -1297,7 +1297,7 @@
         <v>-8.4626</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.857700000000001</v>
+        <v>-2.8577</v>
       </c>
       <c r="O11" t="n">
         <v>-5.604900000000001</v>
@@ -1312,10 +1312,10 @@
         <v>12.0435</v>
       </c>
       <c r="S11" t="n">
-        <v>1.685</v>
+        <v>1.6851</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9522</v>
+        <v>-1.9521</v>
       </c>
       <c r="U11" t="n">
         <v>3.6372</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.621700000000001</v>
+        <v>8.6637</v>
       </c>
       <c r="E12" t="n">
-        <v>5.7845</v>
+        <v>5.3927</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8373</v>
+        <v>3.271</v>
       </c>
       <c r="G12" t="n">
         <v>1.7616</v>
@@ -1390,13 +1390,13 @@
         <v>2.7793</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9903</v>
+        <v>0.0323</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0621</v>
+        <v>-0.4539</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0525</v>
+        <v>0.4862</v>
       </c>
       <c r="V12" t="n">
         <v>4.0904</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1292</v>
+        <v>5.5079</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6234</v>
+        <v>4.0108</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5058</v>
+        <v>1.4971</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5444</v>
+        <v>5.974</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8837</v>
+        <v>-0.7932</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6607</v>
+        <v>6.7672</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9808</v>
+        <v>5.6081</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7734</v>
+        <v>-0.1375</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2074</v>
+        <v>5.7456</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5636</v>
+        <v>0.3659</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1103</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4533</v>
+        <v>1.0216</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0382</v>
+        <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7655</v>
+        <v>-0.5043</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0396</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.274</v>
+        <v>0.1666</v>
       </c>
       <c r="V13" t="n">
-        <v>4.0915</v>
+        <v>-1.2589</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6002</v>
+        <v>5.2512</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4232</v>
+        <v>1.8193</v>
       </c>
       <c r="F14" t="n">
-        <v>1.177</v>
+        <v>3.4319</v>
       </c>
       <c r="G14" t="n">
-        <v>5.974</v>
+        <v>2.5444</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7932</v>
+        <v>1.8837</v>
       </c>
       <c r="I14" t="n">
-        <v>6.7672</v>
+        <v>0.6607</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6081</v>
+        <v>1.9808</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1375</v>
+        <v>1.7734</v>
       </c>
       <c r="L14" t="n">
-        <v>5.7456</v>
+        <v>0.2074</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3659</v>
+        <v>0.5636</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.1103</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0216</v>
+        <v>0.4533</v>
       </c>
       <c r="P14" t="n">
-        <v>1.297</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2234</v>
+        <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4119</v>
+        <v>-0.6435</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2584</v>
+        <v>-0.8437</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1535</v>
+        <v>0.2002</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2589</v>
+        <v>4.0915</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.4616</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1242</v>
+        <v>0.0498</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9104</v>
+        <v>-0.8125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0346</v>
+        <v>0.8622</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5866</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1375</v>
+        <v>0.0631</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.332</v>
+        <v>-0.2341</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4695</v>
+        <v>0.2972</v>
       </c>
       <c r="V16" t="n">
         <v>0.9439</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6016</v>
+        <v>-0.3805</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2465</v>
+        <v>-1.1486</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6449</v>
+        <v>0.768</v>
       </c>
       <c r="G17" t="n">
         <v>0.2022</v>
@@ -1780,13 +1780,13 @@
         <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6926</v>
+        <v>-0.4716</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3096</v>
+        <v>-0.1865</v>
       </c>
       <c r="V17" t="n">
         <v>0.63</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8869</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>-1.1712</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2843</v>
+        <v>0.3582</v>
       </c>
       <c r="G18" t="n">
         <v>1.1732</v>
@@ -1858,13 +1858,13 @@
         <v>2.4087</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="T18" t="n">
         <v>-0.715</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6337</v>
+        <v>0.7075</v>
       </c>
       <c r="V18" t="n">
         <v>-3.461</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SINATRA VAZQUEZ</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9628</v>
+        <v>-1.0274</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3122</v>
+        <v>-1.689</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3494</v>
+        <v>0.6616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5624</v>
+        <v>-1.3197</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08939999999999999</v>
+        <v>-2.1077</v>
       </c>
       <c r="I19" t="n">
-        <v>0.473</v>
+        <v>0.788</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1385</v>
+        <v>-1.0847</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0342</v>
+        <v>-1.2198</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1043</v>
+        <v>0.1351</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4239</v>
+        <v>-0.235</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0552</v>
+        <v>-0.8878</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3687</v>
+        <v>0.6529</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3636</v>
+        <v>-0.2074</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1057</v>
+        <v>0.0078</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2579</v>
+        <v>-0.2151</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8888</v>
+        <v>0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>M. SINATRA VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0279</v>
+        <v>-1.0843</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.591</v>
+        <v>-1.606</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5631</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3197</v>
+        <v>0.5624</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1077</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.788</v>
+        <v>0.473</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0847</v>
+        <v>0.1385</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2198</v>
+        <v>0.0342</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1351</v>
+        <v>0.1043</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.235</v>
+        <v>0.4239</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8878</v>
+        <v>0.0552</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6529</v>
+        <v>0.3687</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2079</v>
+        <v>0.2422</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1057</v>
+        <v>-0.1881</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3136</v>
+        <v>0.4303</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3144</v>
+        <v>-1.8888</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8501</v>
+        <v>-2.0214</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3168</v>
+        <v>-3.5127</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4667</v>
+        <v>1.4913</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3512</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0172</v>
+        <v>-0.1884</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0413</v>
+        <v>0.0659</v>
       </c>
       <c r="V21" t="n">
         <v>0.63</v>
@@ -2128,16 +2128,16 @@
         <v>15.7122</v>
       </c>
       <c r="E22" t="n">
-        <v>2.849200000000001</v>
+        <v>2.849</v>
       </c>
       <c r="F22" t="n">
-        <v>12.8631</v>
+        <v>12.863</v>
       </c>
       <c r="G22" t="n">
         <v>10.5265</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6964000000000005</v>
+        <v>0.6964000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>9.8299</v>
@@ -2146,10 +2146,10 @@
         <v>8.4626</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8579</v>
+        <v>2.857899999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>5.604899999999999</v>
+        <v>5.604900000000001</v>
       </c>
       <c r="M22" t="n">
         <v>2.0638</v>
@@ -2158,7 +2158,7 @@
         <v>-2.1612</v>
       </c>
       <c r="O22" t="n">
-        <v>4.225</v>
+        <v>4.225000000000001</v>
       </c>
       <c r="P22" t="n">
         <v>2.7794</v>
@@ -2170,22 +2170,22 @@
         <v>14.8229</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.685</v>
+        <v>-1.6851</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.6371</v>
+        <v>-3.6373</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9522</v>
+        <v>1.9523</v>
       </c>
       <c r="V22" t="n">
-        <v>4.091499999999999</v>
+        <v>4.091500000000001</v>
       </c>
       <c r="W22" t="n">
         <v>10.0675</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.976</v>
+        <v>-5.975999999999999</v>
       </c>
     </row>
   </sheetData>
